--- a/output/pdf_financials_xlsx/WWT.xlsx
+++ b/output/pdf_financials_xlsx/WWT.xlsx
@@ -1357,7 +1357,7 @@
         <v>-0.024912</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-2.369</v>
@@ -1677,7 +1677,7 @@
         <v>-0.024912</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-2.369</v>
@@ -1866,7 +1866,7 @@
         <v>-0.024912</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-2.369</v>
@@ -2196,7 +2196,7 @@
         <v>-0.024912</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-2.369</v>
@@ -2322,7 +2322,7 @@
         <v>-0.024912</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.463</v>
+        <v>-0.371</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-2.292</v>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>3.829928033749689</v>
+        <v>-3.068905616676317</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-23.80556709597009</v>
@@ -2468,7 +2468,7 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>3.449416825213004</v>
+        <v>-3.449416825213004</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>-24.6053178230162</v>
@@ -6251,34 +6251,34 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.09324</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.09324</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>1.544</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>2.905</v>
+        <v>2.998</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>2.946</v>
+        <v>2.994</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>6.78</v>
+        <v>7.032</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>7.307</v>
+        <v>7.507</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>7.54</v>
+        <v>7.727</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>7.54</v>
+        <v>7.728</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>7.54</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="93">
@@ -6630,7 +6630,7 @@
         <v>-0.024912</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-2.369</v>
@@ -10736,7 +10736,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -16374,7 +16378,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -18794,7 +18802,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -23232,7 +23244,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -24496,7 +24512,11 @@
           <t>Share-based payments reserve 5</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -25232,7 +25252,11 @@
           <t>Share-based payments reserve 5</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -41308,7 +41332,7 @@
         </is>
       </c>
       <c r="O309" s="5" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="P309" s="5" t="n">
         <v>-2.369</v>
@@ -46621,7 +46645,7 @@
         <v>-0.088796</v>
       </c>
       <c r="J360" s="5" t="n">
-        <v>0.026602</v>
+        <v>-0.026602</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
@@ -58630,7 +58654,7 @@
         </is>
       </c>
       <c r="O474" s="5" t="n">
-        <v>0.417</v>
+        <v>-0.417</v>
       </c>
       <c r="P474" s="5" t="n">
         <v>-2.369</v>

--- a/output/pdf_financials_xlsx/WWT.xlsx
+++ b/output/pdf_financials_xlsx/WWT.xlsx
@@ -949,37 +949,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.053053</v>
+        <v>0.235885</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.010846</v>
+        <v>0.079667</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.019027</v>
+        <v>0.118363</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.044204</v>
+        <v>0.118537</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.007012</v>
+        <v>0.118537</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.009169999999999999</v>
+        <v>0.027087</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.006843</v>
+        <v>0.042615</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.006452</v>
+        <v>0.016291</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.008022</v>
+        <v>0.025858</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.007993999999999999</v>
+        <v>0.024912</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.228</v>
+        <v>0.029982</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>1.855</v>
@@ -1012,34 +1012,34 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.053053</v>
+        <v>-0.235885</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.010846</v>
+        <v>-0.079667</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.019027</v>
+        <v>-0.118363</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.044204</v>
+        <v>-0.118537</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.007012</v>
+        <v>-0.118537</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.009169999999999999</v>
+        <v>-0.027087</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.006843</v>
+        <v>-0.042615</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.006452</v>
+        <v>-0.016291</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.008022</v>
+        <v>-0.025858</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.007993999999999999</v>
+        <v>-0.024912</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>0.613</v>
@@ -1087,16 +1087,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015335</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000485</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000451</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000136</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2178,16 +2178,16 @@
         <v>-0.113219</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.088796</v>
+        <v>-0.073461</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.026602</v>
+        <v>-0.026117</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.042164</v>
+        <v>-0.041713</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.016155</v>
+        <v>-0.016019</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.025858</v>
@@ -2304,16 +2304,16 @@
         <v>-0.113219</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.088796</v>
+        <v>-0.073461</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.026602</v>
+        <v>-0.026117</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.042164</v>
+        <v>-0.041713</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.016155</v>
+        <v>-0.016019</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.025858</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.523236</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.441056</v>
@@ -2612,13 +2612,13 @@
         <v>0.043478</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004025</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001291</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.004523</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.233</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.523236</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.441056</v>
@@ -2734,13 +2734,13 @@
         <v>0.043478</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004025</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001291</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.004523</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.233</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.5344640000000001</v>
+        <v>0.011228</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.035</v>
@@ -8166,22 +8166,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.031</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="S124" s="3" t="n">
         <v>0</v>
@@ -8227,22 +8227,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.031</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="S125" s="3" t="n">
         <v>0</v>
@@ -23780,7 +23780,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -26110,7 +26110,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -31412,7 +31412,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
@@ -33894,7 +33894,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -59732,7 +59736,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -59781,10 +59785,10 @@
         </is>
       </c>
       <c r="N485" s="5" t="n">
-        <v>-0.024912</v>
+        <v>0.024912</v>
       </c>
       <c r="O485" s="5" t="n">
-        <v>-0.029982</v>
+        <v>0.029982</v>
       </c>
       <c r="P485" t="inlineStr">
         <is>
@@ -60160,7 +60164,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -60576,7 +60580,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -61194,7 +61198,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -61620,7 +61624,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -61728,7 +61732,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -62458,7 +62462,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -63194,7 +63198,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E518" s="5" t="n">

--- a/output/pdf_financials_xlsx/WWT.xlsx
+++ b/output/pdf_financials_xlsx/WWT.xlsx
@@ -669,10 +669,8 @@
       <c r="M5" s="3" t="n">
         <v>8.422000000000001</v>
       </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>13.199</v>
@@ -795,10 +793,8 @@
       <c r="M7" s="3" t="n">
         <v>1.855</v>
       </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0</v>
@@ -858,10 +854,8 @@
       <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
@@ -921,10 +915,8 @@
       <c r="M9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>0</v>
@@ -984,10 +976,8 @@
       <c r="M10" s="3" t="n">
         <v>1.855</v>
       </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>0</v>
@@ -1110,10 +1100,8 @@
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0.193</v>
@@ -1173,10 +1161,8 @@
       <c r="M13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>-0</v>
@@ -1236,10 +1222,8 @@
       <c r="M14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>0</v>
@@ -1299,10 +1283,8 @@
       <c r="M15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>0</v>
@@ -1362,10 +1344,8 @@
       <c r="M16" s="3" t="n">
         <v>-2.369</v>
       </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" s="3" t="n">
+        <v>-1.166</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-5303</v>
@@ -1425,10 +1405,8 @@
       <c r="M17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0</v>
@@ -1682,10 +1660,8 @@
       <c r="M20" s="3" t="n">
         <v>-2.369</v>
       </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N20" s="3" t="n">
+        <v>-1.166</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-5303</v>
@@ -1745,10 +1721,8 @@
       <c r="M21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>0</v>
@@ -1808,10 +1782,8 @@
       <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>-0.109</v>
@@ -2201,10 +2173,8 @@
       <c r="M27" s="3" t="n">
         <v>-2.369</v>
       </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N27" s="3" t="n">
+        <v>-1.166</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-5303.193</v>
@@ -2264,10 +2234,8 @@
       <c r="M28" s="3" t="n">
         <v>0.077</v>
       </c>
-      <c r="N28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N28" s="3" t="n">
+        <v>0.139</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>194</v>
@@ -2327,10 +2295,8 @@
       <c r="M29" s="3" t="n">
         <v>-2.292</v>
       </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N29" s="3" t="n">
+        <v>-1.027</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-5109.193</v>
@@ -2473,10 +2439,8 @@
       <c r="M31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -4881,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0</v>
@@ -4942,10 +4906,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0</v>
@@ -5186,10 +5150,10 @@
         <v>1.412</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>2.055</v>
+        <v>2.038</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.659</v>
+        <v>2.626</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>2.045</v>
@@ -5519,10 +5483,10 @@
         <v>-0.03687943262411347</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.005420054200542005</v>
+        <v>0.01463414634146342</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>-0.01841432225063938</v>
+        <v>-0.03529411764705882</v>
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
@@ -6728,10 +6692,10 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00601</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00967</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -6743,10 +6707,10 @@
         <v>0</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.006663</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000831</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -7051,7 +7015,7 @@
         <v>-0.039589</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.023955</v>
+        <v>0.023124</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0.027844</v>
@@ -7487,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>0</v>
+        <v>-0.363</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>0</v>
+        <v>1.415</v>
       </c>
       <c r="O113" s="3" t="n">
         <v>0</v>
@@ -8937,7 +8901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V526"/>
+  <dimension ref="A1:V530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12492,7 +12456,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -41070,7 +41038,11 @@
           <t>Acquisition of business (Note 7)</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -42236,7 +42208,11 @@
           <t>Acquisition of business (Note 5)</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -45372,7 +45348,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -47990,7 +47970,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -48826,7 +48810,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -57224,12 +57212,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Revenues:                                           16</t>
+          <t>Level 1        Level 2      Level 3     Total</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Services Projects</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
@@ -57283,21 +57271,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O461" s="5" t="n">
-        <v>6.382</v>
-      </c>
-      <c r="P461" s="5" t="n">
-        <v>4.178</v>
-      </c>
-      <c r="Q461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q461" s="5" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="R461" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -57328,12 +57316,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Revenues:                                           16</t>
+          <t>Level 1        Level 2      Level 3     Total</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>Warrants - -</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
@@ -57387,21 +57375,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O462" s="5" t="n">
-        <v>5.707</v>
-      </c>
-      <c r="P462" s="5" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="Q462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q462" s="5" t="n">
+        <v>-5.037</v>
+      </c>
+      <c r="R462" s="5" t="n">
+        <v>-5.037</v>
       </c>
       <c r="S462" t="inlineStr">
         <is>
@@ -57432,19 +57420,15 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Revenues:                                           16</t>
+          <t>Level 1        Level 2       Level 3     Total</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Total revenues</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -57495,21 +57479,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O463" s="5" t="n">
-        <v>12.089</v>
-      </c>
-      <c r="P463" s="5" t="n">
-        <v>9.628</v>
-      </c>
-      <c r="Q463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q463" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R463" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="S463" t="inlineStr">
         <is>
@@ -57540,12 +57524,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Cost of revenues:                                     17</t>
+          <t>Level 1        Level 2       Level 3     Total</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Services Projects</t>
+          <t>Warrants - -</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
@@ -57599,21 +57583,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O464" s="5" t="n">
-        <v>5.204</v>
-      </c>
-      <c r="P464" s="5" t="n">
-        <v>3.681</v>
-      </c>
-      <c r="Q464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q464" s="5" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="R464" s="5" t="n">
+        <v>-0.052</v>
       </c>
       <c r="S464" t="inlineStr">
         <is>
@@ -57644,12 +57628,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Cost of revenues:                                     17</t>
+          <t>Revenues:                                           16</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>Services Projects</t>
         </is>
       </c>
       <c r="D465" t="inlineStr"/>
@@ -57704,10 +57688,10 @@
         </is>
       </c>
       <c r="O465" s="5" t="n">
-        <v>5.044</v>
+        <v>6.382</v>
       </c>
       <c r="P465" s="5" t="n">
-        <v>4.741</v>
+        <v>4.178</v>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
@@ -57748,12 +57732,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Cost of revenues:                                     17</t>
+          <t>Revenues:                                           16</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Total cost of revenues</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -57808,10 +57792,10 @@
         </is>
       </c>
       <c r="O466" s="5" t="n">
-        <v>10.248</v>
+        <v>5.707</v>
       </c>
       <c r="P466" s="5" t="n">
-        <v>8.422000000000001</v>
+        <v>5.45</v>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
@@ -57852,17 +57836,17 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Cost of revenues:                                     17</t>
+          <t>Revenues:                                           16</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Total revenues</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -57916,10 +57900,10 @@
         </is>
       </c>
       <c r="O467" s="5" t="n">
-        <v>1.841</v>
+        <v>12.089</v>
       </c>
       <c r="P467" s="5" t="n">
-        <v>1.206</v>
+        <v>9.628</v>
       </c>
       <c r="Q467" t="inlineStr">
         <is>
@@ -57965,7 +57949,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Listing expenses 4</t>
+          <t>Services Projects</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
@@ -58019,13 +58003,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O468" s="5" t="n">
+        <v>5.204</v>
       </c>
       <c r="P468" s="5" t="n">
-        <v>1.727</v>
+        <v>3.681</v>
       </c>
       <c r="Q468" t="inlineStr">
         <is>
@@ -58071,14 +58053,10 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses 18</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Products</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -58130,10 +58108,10 @@
         </is>
       </c>
       <c r="O469" s="5" t="n">
-        <v>1.228</v>
+        <v>5.044</v>
       </c>
       <c r="P469" s="5" t="n">
-        <v>1.855</v>
+        <v>4.741</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -58179,14 +58157,10 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Operating profit (loss)</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Total cost of revenues</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -58238,10 +58212,10 @@
         </is>
       </c>
       <c r="O470" s="5" t="n">
-        <v>0.613</v>
+        <v>10.248</v>
       </c>
       <c r="P470" s="5" t="n">
-        <v>-2.376</v>
+        <v>8.422000000000001</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -58282,15 +58256,19 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Financial expenses                                     19                (146 )                 (72)</t>
+          <t>Cost of revenues:                                     17</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Financial income 19</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -58342,10 +58320,10 @@
         </is>
       </c>
       <c r="O471" s="5" t="n">
-        <v>0.004</v>
+        <v>1.841</v>
       </c>
       <c r="P471" s="5" t="n">
-        <v>0.097</v>
+        <v>1.206</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -58386,12 +58364,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Financial expenses                                     19                (146 )                 (72)</t>
+          <t>Cost of revenues:                                     17</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Profit (loss) before taxes on income</t>
+          <t>Listing expenses 4</t>
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
@@ -58445,11 +58423,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O472" s="5" t="n">
-        <v>0.547</v>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P472" s="5" t="n">
-        <v>-2.435</v>
+        <v>1.727</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -58490,15 +58470,19 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Financial expenses                                     19                (146 )                 (72)</t>
+          <t>Cost of revenues:                                     17</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Tax on income (recovery) 20 (</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr"/>
+          <t>Selling, general and administrative expenses 18</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -58550,10 +58534,10 @@
         </is>
       </c>
       <c r="O473" s="5" t="n">
-        <v>0.13</v>
+        <v>1.228</v>
       </c>
       <c r="P473" s="5" t="n">
-        <v>0.066</v>
+        <v>1.855</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -58594,17 +58578,17 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Financial expenses                                     19                (146 )                 (72)</t>
+          <t>Cost of revenues:                                     17</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Profit (loss) for the period</t>
+          <t>Operating profit (loss)</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -58658,10 +58642,10 @@
         </is>
       </c>
       <c r="O474" s="5" t="n">
-        <v>-0.417</v>
+        <v>0.613</v>
       </c>
       <c r="P474" s="5" t="n">
-        <v>-2.369</v>
+        <v>-2.376</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -58702,12 +58686,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Financial expenses                                     19                (146 )                 (72)</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences</t>
+          <t>Financial income 19</t>
         </is>
       </c>
       <c r="D475" t="inlineStr"/>
@@ -58761,13 +58745,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O475" s="5" t="n">
+        <v>0.004</v>
       </c>
       <c r="P475" s="5" t="n">
-        <v>0.061</v>
+        <v>0.097</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -58808,12 +58790,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Financial expenses                                     19                (146 )                 (72)</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Profit (loss) before taxes on income</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
@@ -58867,13 +58849,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O476" s="5" t="n">
+        <v>0.547</v>
       </c>
       <c r="P476" s="5" t="n">
-        <v>0.061</v>
+        <v>-2.435</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -58914,12 +58894,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Other comprehensive expense</t>
+          <t>Financial expenses                                     19                (146 )                 (72)</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Net comprehensive income (loss)</t>
+          <t>Tax on income (recovery) 20 (</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
@@ -58974,10 +58954,10 @@
         </is>
       </c>
       <c r="O477" s="5" t="n">
-        <v>0.417</v>
+        <v>0.13</v>
       </c>
       <c r="P477" s="5" t="n">
-        <v>-2.308</v>
+        <v>0.066</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -59018,15 +58998,19 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Basic profit (loss) per share</t>
+          <t>Financial expenses                                     19                (146 )                 (72)</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Attributable to shareholders (*): ( 0. 027) 0.</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr"/>
+          <t>Profit (loss) for the period</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -59078,10 +59062,10 @@
         </is>
       </c>
       <c r="O478" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.417</v>
       </c>
       <c r="P478" s="5" t="n">
-        <v>0</v>
+        <v>-2.369</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -59122,19 +59106,15 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Weighted average number of</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding:</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Foreign currency translation differences</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -59185,11 +59165,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O479" s="5" t="n">
-        <v>71.707887</v>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P479" s="5" t="n">
-        <v>87.426889</v>
+        <v>0.061</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -59230,12 +59212,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Diluted profit per share</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Diluted profit per share attributable to shareholders (*): (0.027)</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="D480" t="inlineStr"/>
@@ -59289,11 +59271,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O480" s="5" t="n">
-        <v>5e-06</v>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P480" s="5" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -59334,19 +59318,15 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Diluted profit per share</t>
+          <t>Other comprehensive expense</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Diluted average number of common shares outstanding:</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Net comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -59398,10 +59378,10 @@
         </is>
       </c>
       <c r="O481" s="5" t="n">
-        <v>79.005262</v>
+        <v>0.417</v>
       </c>
       <c r="P481" s="5" t="n">
-        <v>87.426889</v>
+        <v>-2.308</v>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
@@ -59442,19 +59422,15 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Basic profit (loss) per share</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Professional fees 8 $</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Attributable to shareholders (*): ( 0. 027) 0.</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -59490,22 +59466,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L482" s="5" t="n">
-        <v>0.009839000000000001</v>
-      </c>
-      <c r="M482" s="5" t="n">
-        <v>0.017836</v>
-      </c>
-      <c r="N482" s="5" t="n">
-        <v>0.016918</v>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O482" s="5" t="n">
-        <v>0.021437</v>
-      </c>
-      <c r="P482" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006</v>
+      </c>
+      <c r="P482" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q482" t="inlineStr">
         <is>
@@ -59546,56 +59526,74 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>Weighted average number of common shares outstanding:</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E483" s="5" t="n">
-        <v>0.046112</v>
-      </c>
-      <c r="F483" s="5" t="n">
-        <v>0.010224</v>
-      </c>
-      <c r="G483" s="5" t="n">
-        <v>0.015223</v>
-      </c>
-      <c r="H483" s="5" t="n">
-        <v>0.035875</v>
-      </c>
-      <c r="I483" s="5" t="n">
-        <v>0.006595</v>
-      </c>
-      <c r="J483" s="5" t="n">
-        <v>0.00665</v>
-      </c>
-      <c r="K483" s="5" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="L483" s="5" t="n">
-        <v>0.006231</v>
-      </c>
-      <c r="M483" s="5" t="n">
-        <v>0.007643</v>
-      </c>
-      <c r="N483" s="5" t="n">
-        <v>0.007743</v>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O483" s="5" t="n">
-        <v>0.007743</v>
-      </c>
-      <c r="P483" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>71.707887</v>
+      </c>
+      <c r="P483" s="5" t="n">
+        <v>87.426889</v>
       </c>
       <c r="Q483" t="inlineStr">
         <is>
@@ -59636,56 +59634,70 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Diluted profit per share</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E484" s="5" t="n">
-        <v>0.006941</v>
-      </c>
-      <c r="F484" s="5" t="n">
-        <v>0.000622</v>
-      </c>
-      <c r="G484" s="5" t="n">
-        <v>0.003804</v>
-      </c>
-      <c r="H484" s="5" t="n">
-        <v>0.008329</v>
-      </c>
-      <c r="I484" s="5" t="n">
-        <v>0.000417</v>
-      </c>
-      <c r="J484" s="5" t="n">
-        <v>0.00252</v>
-      </c>
-      <c r="K484" s="5" t="n">
-        <v>0.001343</v>
-      </c>
-      <c r="L484" s="5" t="n">
-        <v>0.000221</v>
-      </c>
-      <c r="M484" s="5" t="n">
-        <v>0.000379</v>
-      </c>
-      <c r="N484" s="5" t="n">
-        <v>0.000251</v>
+          <t>Diluted profit per share attributable to shareholders (*): (0.027)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O484" s="5" t="n">
-        <v>0.000802</v>
-      </c>
-      <c r="P484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-06</v>
+      </c>
+      <c r="P484" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q484" t="inlineStr">
         <is>
@@ -59726,17 +59738,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Diluted profit per share</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Diluted average number of common shares outstanding:</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -59784,16 +59796,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N485" s="5" t="n">
-        <v>0.024912</v>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O485" s="5" t="n">
-        <v>0.029982</v>
-      </c>
-      <c r="P485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>79.005262</v>
+      </c>
+      <c r="P485" s="5" t="n">
+        <v>87.426889</v>
       </c>
       <c r="Q485" t="inlineStr">
         <is>
@@ -59839,12 +59851,12 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss $</t>
+          <t>Professional fees 8 $</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -59882,21 +59894,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L486" s="5" t="n">
+        <v>0.009839000000000001</v>
+      </c>
+      <c r="M486" s="5" t="n">
+        <v>0.017836</v>
       </c>
       <c r="N486" s="5" t="n">
-        <v>-0.024912</v>
+        <v>0.016918</v>
       </c>
       <c r="O486" s="5" t="n">
-        <v>-0.029982</v>
+        <v>0.021437</v>
       </c>
       <c r="P486" t="inlineStr">
         <is>
@@ -59942,65 +59950,51 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>– basic and diluted</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="n">
+        <v>0.046112</v>
+      </c>
+      <c r="F487" s="5" t="n">
+        <v>0.010224</v>
+      </c>
+      <c r="G487" s="5" t="n">
+        <v>0.015223</v>
+      </c>
+      <c r="H487" s="5" t="n">
+        <v>0.035875</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>0.006595</v>
+      </c>
+      <c r="J487" s="5" t="n">
+        <v>0.00665</v>
+      </c>
+      <c r="K487" s="5" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="L487" s="5" t="n">
+        <v>0.006231</v>
+      </c>
+      <c r="M487" s="5" t="n">
+        <v>0.007643</v>
       </c>
       <c r="N487" s="5" t="n">
-        <v>3.69</v>
+        <v>0.007743</v>
       </c>
       <c r="O487" s="5" t="n">
-        <v>3.69</v>
+        <v>0.007743</v>
       </c>
       <c r="P487" t="inlineStr">
         <is>
@@ -60046,69 +60040,51 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Loss per Share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>– basic and diluted $</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E488" s="5" t="n">
+        <v>0.006941</v>
+      </c>
+      <c r="F488" s="5" t="n">
+        <v>0.000622</v>
+      </c>
+      <c r="G488" s="5" t="n">
+        <v>0.003804</v>
+      </c>
+      <c r="H488" s="5" t="n">
+        <v>0.008329</v>
+      </c>
+      <c r="I488" s="5" t="n">
+        <v>0.000417</v>
+      </c>
+      <c r="J488" s="5" t="n">
+        <v>0.00252</v>
+      </c>
+      <c r="K488" s="5" t="n">
+        <v>0.001343</v>
+      </c>
+      <c r="L488" s="5" t="n">
+        <v>0.000221</v>
+      </c>
+      <c r="M488" s="5" t="n">
+        <v>0.000379</v>
       </c>
       <c r="N488" s="5" t="n">
-        <v>-7e-09</v>
+        <v>0.000251</v>
       </c>
       <c r="O488" s="5" t="n">
-        <v>-8e-09</v>
+        <v>0.000802</v>
       </c>
       <c r="P488" t="inlineStr">
         <is>
@@ -60159,7 +60135,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Total Expenses</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -60192,25 +60168,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J489" s="5" t="n">
-        <v>0.027087</v>
-      </c>
-      <c r="K489" s="5" t="n">
-        <v>0.042615</v>
-      </c>
-      <c r="L489" s="5" t="n">
-        <v>0.016291</v>
-      </c>
-      <c r="M489" s="5" t="n">
-        <v>0.025858</v>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N489" s="5" t="n">
         <v>0.024912</v>
       </c>
-      <c r="O489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O489" s="5" t="n">
+        <v>0.029982</v>
       </c>
       <c r="P489" t="inlineStr">
         <is>
@@ -60261,7 +60243,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Net Loss and Comprehensive Loss $</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -60294,25 +60276,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J490" s="5" t="n">
-        <v>-0.026602</v>
-      </c>
-      <c r="K490" s="5" t="n">
-        <v>-0.042164</v>
-      </c>
-      <c r="L490" s="5" t="n">
-        <v>-0.016155</v>
-      </c>
-      <c r="M490" s="5" t="n">
-        <v>-0.025858</v>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N490" s="5" t="n">
         <v>-0.024912</v>
       </c>
-      <c r="O490" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O490" s="5" t="n">
+        <v>-0.029982</v>
       </c>
       <c r="P490" t="inlineStr">
         <is>
@@ -60358,7 +60346,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>shares outstanding</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -60407,16 +60395,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M491" s="5" t="n">
-        <v>3.69</v>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N491" s="5" t="n">
         <v>3.69</v>
       </c>
-      <c r="O491" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O491" s="5" t="n">
+        <v>3.69</v>
       </c>
       <c r="P491" t="inlineStr">
         <is>
@@ -60462,12 +60450,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Loss per Share</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>– basic and diluted $</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -60515,16 +60503,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M492" s="5" t="n">
-        <v>-7e-09</v>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N492" s="5" t="n">
         <v>-7e-09</v>
       </c>
-      <c r="O492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O492" s="5" t="n">
+        <v>-8e-09</v>
       </c>
       <c r="P492" t="inlineStr">
         <is>
@@ -60575,12 +60563,12 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -60608,26 +60596,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J493" s="5" t="n">
+        <v>0.027087</v>
       </c>
       <c r="K493" s="5" t="n">
-        <v>-0.000451</v>
+        <v>0.042615</v>
       </c>
       <c r="L493" s="5" t="n">
-        <v>-0.000136</v>
-      </c>
-      <c r="M493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016291</v>
+      </c>
+      <c r="M493" s="5" t="n">
+        <v>0.025858</v>
+      </c>
+      <c r="N493" s="5" t="n">
+        <v>0.024912</v>
       </c>
       <c r="O493" t="inlineStr">
         <is>
@@ -60683,10 +60665,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Loss per share $</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -60713,21 +60699,19 @@
         </is>
       </c>
       <c r="J494" s="5" t="n">
-        <v>-7e-09</v>
+        <v>-0.026602</v>
       </c>
       <c r="K494" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.042164</v>
       </c>
       <c r="L494" s="5" t="n">
-        <v>-4e-09</v>
+        <v>-0.016155</v>
       </c>
       <c r="M494" s="5" t="n">
-        <v>-7e-09</v>
-      </c>
-      <c r="N494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025858</v>
+      </c>
+      <c r="N494" s="5" t="n">
+        <v>-0.024912</v>
       </c>
       <c r="O494" t="inlineStr">
         <is>
@@ -60778,12 +60762,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>– basic and diluted</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
@@ -60822,16 +60806,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L495" s="5" t="n">
-        <v>3.69</v>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M495" s="5" t="n">
         <v>3.69</v>
       </c>
-      <c r="N495" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N495" s="5" t="n">
+        <v>3.69</v>
       </c>
       <c r="O495" t="inlineStr">
         <is>
@@ -60882,52 +60866,64 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E496" s="5" t="n">
-        <v>0.016551</v>
-      </c>
-      <c r="F496" s="5" t="n">
-        <v>0.033766</v>
-      </c>
-      <c r="G496" s="5" t="n">
-        <v>0.022784</v>
-      </c>
-      <c r="H496" s="5" t="n">
-        <v>0.033292</v>
-      </c>
-      <c r="I496" s="5" t="n">
-        <v>0.022128</v>
-      </c>
-      <c r="J496" s="5" t="n">
-        <v>0.017917</v>
-      </c>
-      <c r="K496" s="5" t="n">
-        <v>0.035772</v>
-      </c>
-      <c r="L496" s="5" t="n">
-        <v>0.009839000000000001</v>
-      </c>
-      <c r="M496" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N496" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M496" s="5" t="n">
+        <v>-7e-09</v>
+      </c>
+      <c r="N496" s="5" t="n">
+        <v>-7e-09</v>
       </c>
       <c r="O496" t="inlineStr">
         <is>
@@ -60983,12 +60979,12 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Loss per share basic and diluted $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -61022,10 +61018,10 @@
         </is>
       </c>
       <c r="K497" s="5" t="n">
-        <v>-1.1e-08</v>
+        <v>-0.000451</v>
       </c>
       <c r="L497" s="5" t="n">
-        <v>-4e-09</v>
+        <v>-0.000136</v>
       </c>
       <c r="M497" t="inlineStr">
         <is>
@@ -61086,12 +61082,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares Outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Loss per share $</t>
         </is>
       </c>
       <c r="D498" t="inlineStr"/>
@@ -61121,18 +61117,16 @@
         </is>
       </c>
       <c r="J498" s="5" t="n">
-        <v>3.69</v>
+        <v>-7e-09</v>
       </c>
       <c r="K498" s="5" t="n">
-        <v>3.69</v>
+        <v>-1e-08</v>
       </c>
       <c r="L498" s="5" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="M498" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-09</v>
+      </c>
+      <c r="M498" s="5" t="n">
+        <v>-7e-09</v>
       </c>
       <c r="N498" t="inlineStr">
         <is>
@@ -61188,19 +61182,15 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Outstanding</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Interest income (</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -61226,21 +61216,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J499" s="5" t="n">
-        <v>-0.000485</v>
-      </c>
-      <c r="K499" s="5" t="n">
-        <v>0.000451</v>
-      </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L499" s="5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="M499" s="5" t="n">
+        <v>3.69</v>
       </c>
       <c r="N499" t="inlineStr">
         <is>
@@ -61296,52 +61286,42 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying qualifying transaction</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr"/>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E500" s="5" t="n">
+        <v>0.016551</v>
+      </c>
+      <c r="F500" s="5" t="n">
+        <v>0.033766</v>
+      </c>
+      <c r="G500" s="5" t="n">
+        <v>0.022784</v>
+      </c>
+      <c r="H500" s="5" t="n">
+        <v>0.033292</v>
       </c>
       <c r="I500" s="5" t="n">
-        <v>0.015479</v>
-      </c>
-      <c r="J500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022128</v>
+      </c>
+      <c r="J500" s="5" t="n">
+        <v>0.017917</v>
+      </c>
+      <c r="K500" s="5" t="n">
+        <v>0.035772</v>
+      </c>
+      <c r="L500" s="5" t="n">
+        <v>0.009839000000000001</v>
       </c>
       <c r="M500" t="inlineStr">
         <is>
@@ -61402,15 +61382,19 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying transaction submission withdrawn</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr"/>
+          <t>Loss per share basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -61431,23 +61415,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I501" s="5" t="n">
-        <v>-0.03</v>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K501" s="5" t="n">
+        <v>-1.1e-08</v>
+      </c>
+      <c r="L501" s="5" t="n">
+        <v>-4e-09</v>
       </c>
       <c r="M501" t="inlineStr">
         <is>
@@ -61508,12 +61490,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying</t>
+          <t>Weighted Average Number of Shares Outstanding</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Loan impairment provision (note 3)</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D502" t="inlineStr"/>
@@ -61537,23 +61519,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I502" s="5" t="n">
-        <v>0.08951199999999999</v>
-      </c>
-      <c r="J502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J502" s="5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K502" s="5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="L502" s="5" t="n">
+        <v>3.69</v>
       </c>
       <c r="M502" t="inlineStr">
         <is>
@@ -61614,17 +61592,17 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Interest income (</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -61647,16 +61625,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I503" s="5" t="n">
-        <v>0.118537</v>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J503" s="5" t="n">
-        <v>0.027087</v>
-      </c>
-      <c r="K503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000485</v>
+      </c>
+      <c r="K503" s="5" t="n">
+        <v>0.000451</v>
       </c>
       <c r="L503" t="inlineStr">
         <is>
@@ -61722,19 +61700,15 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying</t>
+          <t>Expenses relating to identifying</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Interest income (</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Expenses relating to identifying qualifying transaction</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -61756,10 +61730,12 @@
         </is>
       </c>
       <c r="I504" s="5" t="n">
-        <v>-0.015335</v>
-      </c>
-      <c r="J504" s="5" t="n">
-        <v>0.000485</v>
+        <v>0.015479</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
@@ -61835,14 +61811,10 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Refund of filing fees for qualifying transaction submission withdrawn</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -61864,10 +61836,12 @@
         </is>
       </c>
       <c r="I505" s="5" t="n">
-        <v>-0.088796</v>
-      </c>
-      <c r="J505" s="5" t="n">
-        <v>-0.026602</v>
+        <v>-0.03</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
@@ -61938,32 +61912,42 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>diluted</t>
+          <t>Refund of filing fees for qualifying</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Loss per share $</t>
+          <t>Loan impairment provision (note 3)</t>
         </is>
       </c>
       <c r="D506" t="inlineStr"/>
-      <c r="E506" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="F506" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G506" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H506" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I506" s="5" t="n">
-        <v>-2.4e-08</v>
-      </c>
-      <c r="J506" s="5" t="n">
-        <v>-7e-09</v>
+        <v>0.08951199999999999</v>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
@@ -62034,15 +62018,19 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>Refund of filing fees for qualifying</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Outstanding – Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -62058,14 +62046,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H507" s="5" t="n">
-        <v>3.69</v>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I507" s="5" t="n">
-        <v>3.69</v>
+        <v>0.118537</v>
       </c>
       <c r="J507" s="5" t="n">
-        <v>3.69</v>
+        <v>0.027087</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -62136,15 +62126,19 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying qualifying</t>
+          <t>Refund of filing fees for qualifying</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying qualifying transaction costs</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr"/>
+          <t>Interest income (</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -62160,16 +62154,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H508" s="5" t="n">
-        <v>0.041041</v>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I508" s="5" t="n">
-        <v>0.015479</v>
-      </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.015335</v>
+      </c>
+      <c r="J508" s="5" t="n">
+        <v>0.000485</v>
       </c>
       <c r="K508" t="inlineStr">
         <is>
@@ -62240,15 +62234,19 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying transaction</t>
+          <t>Refund of filing fees for qualifying</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying transaction submission withdrawn</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
@@ -62270,12 +62268,10 @@
         </is>
       </c>
       <c r="I509" s="5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="J509" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.088796</v>
+      </c>
+      <c r="J509" s="5" t="n">
+        <v>-0.026602</v>
       </c>
       <c r="K509" t="inlineStr">
         <is>
@@ -62346,42 +62342,32 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying transaction</t>
+          <t>diluted</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Loan impairment provision (note 3)</t>
+          <t>Loss per share $</t>
         </is>
       </c>
       <c r="D510" t="inlineStr"/>
-      <c r="E510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E510" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="F510" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G510" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H510" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="I510" s="5" t="n">
-        <v>0.08951199999999999</v>
-      </c>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.4e-08</v>
+      </c>
+      <c r="J510" s="5" t="n">
+        <v>-7e-09</v>
       </c>
       <c r="K510" t="inlineStr">
         <is>
@@ -62452,19 +62438,15 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying transaction</t>
+          <t>Weighted Average Number of Shares</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Outstanding – Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -62481,15 +62463,13 @@
         </is>
       </c>
       <c r="H511" s="5" t="n">
-        <v>0.118537</v>
+        <v>3.69</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>0.104131</v>
-      </c>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.69</v>
+      </c>
+      <c r="J511" s="5" t="n">
+        <v>3.69</v>
       </c>
       <c r="K511" t="inlineStr">
         <is>
@@ -62560,12 +62540,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Refund of filing fees for qualifying transaction</t>
+          <t>Expenses relating to identifying qualifying</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Interest and miscellaneous income</t>
+          <t>Expenses relating to identifying qualifying transaction costs</t>
         </is>
       </c>
       <c r="D512" t="inlineStr"/>
@@ -62585,10 +62565,10 @@
         </is>
       </c>
       <c r="H512" s="5" t="n">
-        <v>-0.005318</v>
+        <v>0.041041</v>
       </c>
       <c r="I512" s="5" t="n">
-        <v>-0.015335</v>
+        <v>0.015479</v>
       </c>
       <c r="J512" t="inlineStr">
         <is>
@@ -62669,14 +62649,10 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Refund of filing fees for qualifying transaction submission withdrawn</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -62692,11 +62668,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H513" s="5" t="n">
-        <v>-0.113219</v>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I513" s="5" t="n">
-        <v>-0.088796</v>
+        <v>-0.03</v>
       </c>
       <c r="J513" t="inlineStr">
         <is>
@@ -62772,12 +62750,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Outstanding – Basic and diluted</t>
+          <t>Refund of filing fees for qualifying transaction</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Loss per share $</t>
+          <t>Loan impairment provision (note 3)</t>
         </is>
       </c>
       <c r="D514" t="inlineStr"/>
@@ -62796,11 +62774,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H514" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I514" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.08951199999999999</v>
       </c>
       <c r="J514" t="inlineStr">
         <is>
@@ -62876,35 +62856,39 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Refund of filing fees for qualifying transaction</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr"/>
-      <c r="E515" s="5" t="n">
-        <v>0.058882</v>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G515" s="5" t="n">
-        <v>0.003231</v>
-      </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H515" s="5" t="n">
+        <v>0.118537</v>
+      </c>
+      <c r="I515" s="5" t="n">
+        <v>0.104131</v>
       </c>
       <c r="J515" t="inlineStr">
         <is>
@@ -62980,12 +62964,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying</t>
+          <t>Refund of filing fees for qualifying transaction</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying qualifying transaction costs</t>
+          <t>Interest and miscellaneous income</t>
         </is>
       </c>
       <c r="D516" t="inlineStr"/>
@@ -62999,16 +62983,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G516" s="5" t="n">
-        <v>0.07610500000000001</v>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H516" s="5" t="n">
-        <v>0.041041</v>
-      </c>
-      <c r="I516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005318</v>
+      </c>
+      <c r="I516" s="5" t="n">
+        <v>-0.015335</v>
       </c>
       <c r="J516" t="inlineStr">
         <is>
@@ -63084,35 +63068,39 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying</t>
+          <t>Refund of filing fees for qualifying transaction</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying transaction costs</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F517" s="5" t="n">
-        <v>-0.02137</v>
-      </c>
-      <c r="G517" s="5" t="n">
-        <v>-0.002784</v>
-      </c>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I517" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H517" s="5" t="n">
+        <v>-0.113219</v>
+      </c>
+      <c r="I517" s="5" t="n">
+        <v>-0.088796</v>
       </c>
       <c r="J517" t="inlineStr">
         <is>
@@ -63188,35 +63176,35 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying</t>
+          <t>Outstanding – Basic and diluted</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E518" s="5" t="n">
-        <v>0.235885</v>
-      </c>
-      <c r="F518" s="5" t="n">
-        <v>0.079667</v>
-      </c>
-      <c r="G518" s="5" t="n">
-        <v>0.118363</v>
+          <t>Loss per share $</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H518" s="5" t="n">
-        <v>0.118537</v>
-      </c>
-      <c r="I518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="I518" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="J518" t="inlineStr">
         <is>
@@ -63292,19 +63280,17 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Interest and miscellaneous income</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D519" t="inlineStr"/>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E519" s="5" t="n">
+        <v>0.058882</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -63312,10 +63298,12 @@
         </is>
       </c>
       <c r="G519" s="5" t="n">
-        <v>-0.001754</v>
-      </c>
-      <c r="H519" s="5" t="n">
-        <v>-0.005318</v>
+        <v>0.003231</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
@@ -63396,30 +63384,30 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying</t>
+          <t>Expenses relating to identifying</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E520" s="5" t="n">
-        <v>-0.235885</v>
-      </c>
-      <c r="F520" s="5" t="n">
-        <v>-0.079667</v>
+          <t>Expenses relating to identifying qualifying transaction costs</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G520" s="5" t="n">
-        <v>-0.116609</v>
+        <v>0.07610500000000001</v>
       </c>
       <c r="H520" s="5" t="n">
-        <v>-0.113219</v>
+        <v>0.041041</v>
       </c>
       <c r="I520" t="inlineStr">
         <is>
@@ -63500,26 +63488,30 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Reversal of aborted qualifying</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Outstanding – Basic and diluted</t>
+          <t>Reversal of aborted qualifying transaction costs</t>
         </is>
       </c>
       <c r="D521" t="inlineStr"/>
-      <c r="E521" s="5" t="n">
-        <v>3.305836</v>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F521" s="5" t="n">
-        <v>3.69</v>
+        <v>-0.02137</v>
       </c>
       <c r="G521" s="5" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="H521" s="5" t="n">
-        <v>3.69</v>
+        <v>-0.002784</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
@@ -63600,28 +63592,30 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying</t>
+          <t>Reversal of aborted qualifying</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Expenses relating to identifying qualifying transactions</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E522" s="5" t="n">
-        <v>0.107399</v>
+        <v>0.235885</v>
       </c>
       <c r="F522" s="5" t="n">
-        <v>0.056425</v>
+        <v>0.079667</v>
       </c>
       <c r="G522" s="5" t="n">
-        <v>0.07610500000000001</v>
-      </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.118363</v>
+      </c>
+      <c r="H522" s="5" t="n">
+        <v>0.118537</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
@@ -63707,7 +63701,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Deficit – beginning of year</t>
+          <t>Interest and miscellaneous income</t>
         </is>
       </c>
       <c r="D523" t="inlineStr"/>
@@ -63716,16 +63710,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F523" s="5" t="n">
-        <v>-0.235885</v>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G523" s="5" t="n">
-        <v>-0.315552</v>
-      </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001754</v>
+      </c>
+      <c r="H523" s="5" t="n">
+        <v>-0.005318</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
@@ -63811,25 +63805,25 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Deficit – end of year $</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr"/>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E524" s="5" t="n">
+        <v>-0.235885</v>
       </c>
       <c r="F524" s="5" t="n">
-        <v>-0.315552</v>
+        <v>-0.079667</v>
       </c>
       <c r="G524" s="5" t="n">
-        <v>-0.432161</v>
-      </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.116609</v>
+      </c>
+      <c r="H524" s="5" t="n">
+        <v>-0.113219</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
@@ -63910,32 +63904,26 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Deficit – beginning of period</t>
+          <t>Outstanding – Basic and diluted</t>
         </is>
       </c>
       <c r="D525" t="inlineStr"/>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E525" s="5" t="n">
+        <v>3.305836</v>
       </c>
       <c r="F525" s="5" t="n">
-        <v>-0.235885</v>
-      </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.69</v>
+      </c>
+      <c r="G525" s="5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="H525" s="5" t="n">
+        <v>3.69</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
@@ -64016,97 +64004,513 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Reversal of aborted qualifying</t>
+          <t>Expenses relating to identifying</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Deficit – end of period $</t>
+          <t>Expenses relating to identifying qualifying transactions</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
       <c r="E526" s="5" t="n">
+        <v>0.107399</v>
+      </c>
+      <c r="F526" s="5" t="n">
+        <v>0.056425</v>
+      </c>
+      <c r="G526" s="5" t="n">
+        <v>0.07610500000000001</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Reversal of aborted qualifying</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Deficit – beginning of year</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F527" s="5" t="n">
         <v>-0.235885</v>
       </c>
-      <c r="F526" s="5" t="n">
+      <c r="G527" s="5" t="n">
         <v>-0.315552</v>
       </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V526" t="inlineStr">
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Reversal of aborted qualifying</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Deficit – end of year $</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F528" s="5" t="n">
+        <v>-0.315552</v>
+      </c>
+      <c r="G528" s="5" t="n">
+        <v>-0.432161</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Reversal of aborted qualifying</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Deficit – beginning of period</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr"/>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F529" s="5" t="n">
+        <v>-0.235885</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Reversal of aborted qualifying</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Deficit – end of period $</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
+      <c r="E530" s="5" t="n">
+        <v>-0.235885</v>
+      </c>
+      <c r="F530" s="5" t="n">
+        <v>-0.315552</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V530" t="inlineStr">
         <is>
           <t>-</t>
         </is>
